--- a/records/delivery_records.xlsx
+++ b/records/delivery_records.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="61">
   <si>
     <t>国家</t>
   </si>
@@ -206,6 +206,18 @@
   </si>
   <si>
     <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>Euro Creations Public Company Limited</t>
+  </si>
+  <si>
+    <t>WPS Pro(1Y)</t>
+  </si>
+  <si>
+    <t>GZU1T-MHZ16-4CEG8-MXGXB-G6HVW-A6AVI</t>
   </si>
 </sst>
 </file>
@@ -590,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.0909090909091" customWidth="1"/>
@@ -1119,6 +1131,29 @@
       </c>
       <c r="N26" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>11</v>
+      </c>
+      <c r="N27" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
